--- a/Module_2_Oct_2026/Module2_outline.xlsx
+++ b/Module_2_Oct_2026/Module2_outline.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{C81668DE-A8A6-4010-B6FA-1073236ADCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{626AE1C7-E685-432C-A127-DFDA302AF56C}"/>
   <bookViews>
-    <workbookView xWindow="1357" yWindow="1035" windowWidth="17843" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="180" windowWidth="17842" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Module 2" sheetId="2" r:id="rId1"/>
